--- a/Login-Logout local/cc.xlsx
+++ b/Login-Logout local/cc.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20730"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Office-Works\daily-random-codes\Login-Logout local\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7FBC5A-ECAD-43A3-BD25-340F119E0C4E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -79,7 +85,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -178,6 +184,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -467,7 +476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
@@ -562,7 +571,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
@@ -657,7 +666,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
@@ -728,7 +737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
